--- a/docs/아이디어_후보_분석.xlsx
+++ b/docs/아이디어_후보_분석.xlsx
@@ -502,13 +502,13 @@
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,37 +559,37 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>노릴 상</t>
+          <t>난이도</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>난이도</t>
+          <t>공익성</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>공익성</t>
+          <t>데이터 적합성</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>데이터 적합성</t>
+          <t>차별성</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>차별성</t>
+          <t>실현 가능성</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>실현 가능성</t>
+          <t>총점 (20)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>총점 (20)</t>
+          <t>근거 통계·실제 사례 (웹 검색 확인)</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>도로공사 졸음쉼터 운영·확충 사업, 고속도로 교통정보 앱의 휴게시설 안내, 차량 운전자 졸음경고(DMS·차로이탈경고), 화물차 휴게시간 의무제</t>
+          <t>도로공사 졸음쉼터 237곳 운영(표준 간격 15km), 2026.7 시작한 '휴식포인트'(위드라이브 앱, 15분 이상 쉬면 포인트), 화물차 휴게시간 의무, 차량 졸음경고</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -639,13 +639,11 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>도로공사장상 (대상 도전)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>5</v>
@@ -654,13 +652,15 @@
         <v>5</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" s="2" t="n">
         <v>19</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>2019~2023년 고속도로 사망자 832명 중 71%(591명)가 졸음·주시태만, 2026년 상반기 사망자 95명(전년 대비 35.7%↑) 중 71.6%가 졸음·주시태만 (한국도로공사)</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>화물차 휴게시간 의무제(연속 운전 후 휴식), 화물차 라운지·휴게소 대형차 주차장</t>
+          <t>화물차 '2시간 운전 15분 휴식' 의무화, 국토부 화물차 휴게소 54개소 확충 계획('25~'34)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -709,28 +709,28 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>도로공사장상</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>5</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" s="2" t="n">
         <v>18</v>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>졸음쉼터 232곳 주차면 3,451면 중 대형 587면(17%)뿐이고 일부는 소형 2면을 합친 가변면. 화물차 사망사고 원인의 76%가 졸음·주시태만</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -739,68 +739,68 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>대구 노후 상수관 파손 위험지도</t>
+          <t>수소충전소 고장 예지정비</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>노후 상수관 파손으로 단수·누수(유수율 저하)가 반복되고, 교체 예산은 한정적</t>
+          <t>수소충전소의 잦은 고장과 운영 중단으로 수소차 이용자가 불편을 겪고 보급에도 걸림돌</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>긴급복구공사 이력, 요금민원, 유량·수질, 시설물 정보를 결합해 읍면동별 파손 위험을 예측하고 관로 교체 우선순위를 제시</t>
+          <t>압축기·냉동기·충전기 등 설비 운영 데이터로 이상 징후를 탐지해 고장 전에 정비 시점을 알림</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원: 대구 상수도 긴급복구공사·유량수질·시설물·요금민원·급수공사</t>
+          <t>경북대 첨단기술원: 수소충전소 냉동기·냉각수공급장치·인입판넬·충전기·압축기·우선순위제어반 운영데이터</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>환경부 스마트 관망관리, 지자체 블록별 유수율 관리, 정기 관로 진단</t>
+          <t>충전소 운영정보 안내, 울산 심야충전 대응 강화, 제조사 정기점검</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>기존은 설비 계측 중심. 민원과 복구 이력까지 결합해 '다음에 터질 곳'을 예측</t>
+          <t>기존은 고장 후 운영 중단 공지. 센서 기반 사전 예측으로 가동률을 높임</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>상수도 데이터 7종이 풍부하고 결합하기 좋음</t>
+          <t>AI 기술성이 잘 드러남, 결과가 명확</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>상수도 도메인 지식 필요, 결과가 행정 내부용이라 대중적 임팩트는 약함</t>
+          <t>달성군 1곳 데이터라 일반화에 한계, 설비 도메인 지식 필요</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원장상</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" s="2" t="n">
         <v>17</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>최근 3년간 수소충전소 93곳이 고장으로 총 1,179일 운영 중단, 대구도 충전소 고장·정비 시 운행 차질 보도(2026.9)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -809,53 +809,51 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>상수도 사용 패턴 기반 고립가구 조기발견</t>
+          <t>대구 노후 상수관 파손 위험지도</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>1인 가구가 늘면서 고독사가 사회문제가 됨 (고독사예방법 시행). 위기가구 발굴이 체납·단수 같은 사후 신호에 의존</t>
+          <t>노후 상수관 파손으로 단수·누수(유수율 저하)가 반복되고, 교체 예산은 한정적</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>월별 수도 사용량이 급감하거나 패턴이 바뀌는 가구가 많은 지역을 찾아, 임대주택·소득 정보와 결합해 읍면동 단위 고립위험 지도를 작성</t>
+          <t>긴급복구공사 이력, 요금민원, 유량·수질, 시설물 정보를 결합해 읍면동별 파손 위험을 예측하고 관로 교체 우선순위를 제시</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원: 대구 상수도 고지정보·계량기, 경북개발공사 임대주택 고객정보 / KCB 소득</t>
+          <t>경북대 첨단기술원: 대구 상수도 긴급복구공사·유량수질·시설물·요금민원·급수공사</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>사회보장정보원 위기가구 발굴(단전·단수·체납 정보), 한전 1인가구 안부살핌(전력 사용 패턴), 지자체 IoT 안부 확인</t>
+          <t>K-water 스마트 관망관리(SWNM), 부산 '상수인' AI 플랫폼, 민간 누수감지 IoT</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>기존은 체납·단수처럼 사후 신호 중심. 사용량 '변화 패턴'으로 더 이른 시점에 지역 단위로 탐지</t>
+          <t>기존은 설비 계측 중심. 민원과 복구 이력까지 결합해 '다음에 터질 곳'을 예측</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>사회적 공감도가 매우 높음</t>
+          <t>상수도 데이터 7종이 풍부하고 결합하기 좋음</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>월 단위 검침이라 실시간성이 낮음, 개인정보 민감도를 제안서에서 충분히 설명해야 함</t>
+          <t>상수도 도메인 지식 필요, 결과가 행정 내부용이라 대중적 임팩트는 약함</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원장상 (대상 도전)</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>5</v>
@@ -867,10 +865,12 @@
         <v>4</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>부산은 9,000km 상수관 교체 시기 예측에 AI 도입, 관로 노후도 진단 AI·누수감지 IoT 기업 사례 다수</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -899,7 +899,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>환경부 올바로시스템(폐기물 인계관리), 지자체 처리시설 계획</t>
+          <t>올바로시스템, 지자체 소각장 확충 계획</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -919,28 +919,28 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>환경공단 후원상</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="L6" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>4</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>2026.1부터 수도권 생활폐기물 직매립 금지 시행, 66개 기초지자체 중 33곳이 공공소각 용량 부족으로 민간위탁 필요, 지방 전가 우려</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -949,68 +949,68 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>전북 청년 이탈 조기경보</t>
+          <t>상수도 사용 패턴 기반 고립가구 조기발견</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>지방 소멸이 가속되고 청년 인구가 수도권으로 유출됨</t>
+          <t>1인 가구가 늘면서 고독사가 사회문제가 됨 (고독사예방법 시행). 위기가구 발굴이 체납·단수 같은 사후 신호에 의존</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>국민연금 지역이동량과 사업장 가입자 변동으로 일자리를 따라 이동하는 흐름을 읍면동 단위로 포착하고, 소득·소비 데이터와 결합해 이탈 위험 지역과 원인을 진단</t>
+          <t>월별 수도 사용량이 급감하거나 패턴이 바뀌는 가구가 많은 지역을 찾아, 임대주택·소득 정보와 결합해 읍면동 단위 고립위험 지도를 작성</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>전북·국민연금: 지역이동량, 사업장, 사업장·지역가입자 / KCB 소득, 신한카드 매출, SKT 유동인구</t>
+          <t>경북대 첨단기술원: 대구 상수도 고지정보·계량기, 경북개발공사 임대주택 고객정보 / KCB 소득</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>행안부 인구감소지역 지정과 지방소멸대응기금, 통계청 국내인구이동통계, 전북 청년정책</t>
+          <t>한전 AI 안부살핌(전력+통신 데이터, 32개 기초지자체, 고독사 예방 11건), 복지사각지대 발굴시스템(단전·단수 등 47종)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>기존 통계는 주소 기준 연 단위. 연금 자격 이동으로 일자리 기반 이동을 더 촘촘히 포착</t>
+          <t>기존은 체납·단수처럼 사후 신호 중심. 사용량 '변화 패턴'으로 더 이른 시점에 지역 단위로 탐지</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>지역 현안과 직결, 전북도지사상 경쟁 구도가 명확</t>
+          <t>사회적 공감도가 매우 높음</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>2025년 Re:Career가 같은 기관 데이터를 사용했으니 지역이동량 중심으로 차별화 필요</t>
+          <t>월 단위 검침이라 실시간성이 낮음, 개인정보 민감도를 제안서에서 충분히 설명해야 함</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>전북도지사상</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K7" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="L7" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>복지사각지대 발굴시스템이 47종 위기정보를 쓰며, 복지부가 전기·수도 사용량 변화 추가와 입수주기 단축(2→1개월)을 추진 중</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>고령 보행자 교통사고 위험지수</t>
+          <t>전북 청년 이탈 조기경보</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>초고령사회 진입으로 고령 보행자 사고와 사망 비중이 높음</t>
+          <t>지방 소멸이 가속되고 청년 인구가 수도권으로 유출됨</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>사고 데이터와 연령별 유동인구, 필지·지형을 결합해 고령자 사고 위험지수를 만들고 노인보호구역 추가 지정 후보를 제안</t>
+          <t>국민연금 지역이동량과 사업장 가입자 변동으로 일자리를 따라 이동하는 흐름을 읍면동 단위로 포착하고, 소득·소비 데이터와 결합해 이탈 위험 지역과 원인을 진단</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>한국도로교통공단 교통사고 / SKT 성·연령별 유동인구, LX 국토정보필지·DEM</t>
+          <t>전북·국민연금: 지역이동량, 사업장, 사업장·지역가입자 / KCB 소득, 신한카드 매출, SKT 유동인구</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>도로교통공단 TAAS(교통사고분석시스템), 노인보호구역 제도</t>
+          <t>행안부 인구감소지역·지방소멸대응기금, 통계청 국내인구이동통계, 전북 통계시스템</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>TAAS는 사고 결과 중심. 실제 고령 유동 노출량으로 나눈 위험도로 사고가 아직 적은 잠재 위험 지역까지 찾음</t>
+          <t>기존 통계는 주소 기준 연 단위. 연금 자격 이동으로 일자리 기반 이동을 더 촘촘히 포착</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>공익성 높고 방법론이 명확</t>
+          <t>지역 현안과 직결, 전북도지사상 경쟁 구도가 명확</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>교통사고 데이터의 위치 정밀도 확인 필요</t>
+          <t>2025년 Re:Career가 같은 기관 데이터를 사용했으니 지역이동량 중심으로 차별화 필요</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>도로교통공단 후원상</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K8" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="L8" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>전북 청년 인구 연 약 8,000명 감소(4년간 3만여 명), 전주 제외 13개 시·군 소멸위험, 20대 순이동률 -3.1%로 최대</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1089,68 +1089,68 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>고속도로 사고 대응시간 단축</t>
+          <t>고령 보행자 교통사고 위험지수</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>사고 처리가 늦어지면 정체와 2차 사고가 늘어남</t>
+          <t>초고령사회 진입으로 고령 보행자 사고와 사망 비중이 높음</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>구급차 도착·인명구조·사고처리 소요시간과 도로점유 유형을 분석해 지연 구간을 찾고 견인·구급 거점 배치를 제안</t>
+          <t>사고 데이터와 연령별 유동인구, 필지·지형을 결합해 고령자 사고 위험지수를 만들고 노인보호구역 추가 지정 후보를 제안</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>한국도로공사: 고속도로 교통사고(구급차도착·사고처리 소요시간, 도로점유), 차량통행지표</t>
+          <t>한국도로교통공단 교통사고 / SKT 성·연령별 유동인구, LX 국토정보필지·DEM</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>도로공사 긴급견인 무료서비스, 2차사고 예방 캠페인</t>
+          <t>TAAS 교통사고분석시스템, 노인보호구역(30km/h) 제도</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>기존은 일괄 운영. 구간별 지연 원인을 데이터로 진단</t>
+          <t>TAAS는 사고 결과 중심. 실제 고령 유동 노출량으로 나눈 위험도로 사고가 아직 적은 잠재 위험 지역까지 찾음</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>데이터 컬럼이 풍부하고 바로 분석 가능</t>
+          <t>공익성 높고 방법론이 명확</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>2025년 구해줘헬기즈(중증외상 이송)와 겹쳐 차별성이 약함</t>
+          <t>교통사고 데이터의 위치 정밀도 확인 필요</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>도로공사장상</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>2025년 보행 사망자 920명(3.8%↑) 중 65세 이상이 절반 이상, 고령 보행자 사고 11,498건(1.7%↑)</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1159,68 +1159,68 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>사용후 배터리 재사용 매칭</t>
+          <t>고속도로 사고 대응시간 단축</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>전기차 보급 확대로 사용후 배터리가 급증할 예정인데, 재사용 판단과 수요 연결이 비효율적</t>
+          <t>사고 처리가 늦어지면 정체와 2차 사고가 늘어남</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>성능평가 결과로 재사용 등급을 예측하고, 지역별 EV 충전 수요와 연결해 재사용 ESS(충전 보조 저장장치) 설치 후보지를 제안</t>
+          <t>구급차 도착·인명구조·사고처리 소요시간과 도로점유 유형을 분석해 지연 구간을 찾고 견인·구급 거점 배치를 제안</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>한국환경공단: 전기차 폐배터리 성능평가 / 한국전력공사: 법정동별 시간대 EV 충전전력량</t>
+          <t>한국도로공사: 고속도로 교통사고(구급차도착·사고처리 소요시간, 도로점유), 차량통행지표</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>환경부 미래폐자원 거점수거센터, 사용후 배터리 성능평가 제도, 민간 배터리 재사용 기업</t>
+          <t>도로공사 무료 긴급견인(1588-2504, 24시간), 2차사고 예방 행동요령 캠페인</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>기존은 수거·평가까지만. 평가 결과와 지역 수요를 연결하는 순환 모델을 제시</t>
+          <t>기존은 일괄 운영. 구간별 지연 원인을 데이터로 진단</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>미래 이슈이고 경쟁팀이 적을 가능성이 큼</t>
+          <t>데이터 컬럼이 풍부하고 바로 분석 가능</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>성능평가 데이터의 규모 확인 필요, 수요 매칭 논리를 설득력 있게 짜야 함</t>
+          <t>2025년 구해줘헬기즈(중증외상 이송)와 겹쳐 차별성이 약함</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>환경공단 후원상 / 한전장상</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>2차사고 치사율이 일반사고의 약 6배, 최근 5년 사망자 784명 중 138명(18%)이 2차사고</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1229,68 +1229,68 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>연안침식이 관광 경제에 주는 영향</t>
+          <t>사용후 배터리 재사용 매칭</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>기후변화로 연안침식이 심해져 해수욕장 백사장이 줄고 지역 관광에도 영향</t>
+          <t>전기차 보급 확대로 사용후 배터리가 급증할 예정인데, 재사용 판단과 수요 연결이 비효율적</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>해빈폭·단면적 변화와 주변 유동인구·카드매출을 결합해 침식의 경제 피해를 추정하고 복원 투자 우선순위를 제시</t>
+          <t>성능평가 결과로 재사용 등급을 예측하고, 지역별 EV 충전 수요와 연결해 재사용 ESS(충전 보조 저장장치) 설치 후보지를 제안</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>NIA: 연안침식 모니터링, 해수욕장 해빈폭·단면적 / SKT 유동인구, 신한카드 매출</t>
+          <t>한국환경공단: 전기차 폐배터리 성능평가 / 한국전력공사: 법정동별 시간대 EV 충전전력량</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>해양수산부 연안침식 실태조사(등급 평가), 연안정비사업</t>
+          <t>기후부 미래폐자원 거점수거센터, 민간 공급(연 1,500개 목표), 2027 탈거 전 성능평가 의무화</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>기존은 물리적 침식 등급 중심. 경제 피해를 결합해 투자 우선순위를 판단</t>
+          <t>기존은 수거·평가까지만. 평가 결과와 지역 수요를 연결하는 순환 모델을 제시</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>참신하고 기후 이슈와 연결</t>
+          <t>미래 이슈이고 경쟁팀이 적을 가능성이 큼</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>해수욕장 주변 데이터 매칭 범위가 불확실, 인과 분석 난이도가 높음</t>
+          <t>성능평가 데이터의 규모 확인 필요, 수요 매칭 논리를 설득력 있게 짜야 함</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>NIA장상</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
           <t>상</t>
         </is>
       </c>
+      <c r="K11" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L11" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>2021년부터 권역별 거점수거센터 6곳 운영, 1시간 신속 성능평가 도입, 대구·경남 거점 추가, 2027년 성능평가 의무화 예정</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1299,53 +1299,51 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>수소충전소 고장 예지정비</t>
+          <t>연안침식이 관광 경제에 주는 영향</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>수소충전소의 잦은 고장과 운영 중단으로 수소차 이용자가 불편을 겪고 보급에도 걸림돌</t>
+          <t>기후변화로 연안침식이 심해져 해수욕장 백사장이 줄고 지역 관광에도 영향</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>압축기·냉동기·충전기 등 설비 운영 데이터로 이상 징후를 탐지해 고장 전에 정비 시점을 알림</t>
+          <t>해빈폭·단면적 변화와 주변 유동인구·카드매출을 결합해 침식의 경제 피해를 추정하고 복원 투자 우선순위를 제시</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원: 수소충전소 냉동기·냉각수공급장치·인입판넬·충전기·압축기·우선순위제어반 운영데이터</t>
+          <t>NIA: 연안침식 모니터링, 해수욕장 해빈폭·단면적 / SKT 유동인구, 신한카드 매출</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>수소충전소 운영 현황 안내(하이넷 등), 제조사 정기 점검</t>
+          <t>해수부 연안침식 실태조사(A~D 등급), 연안포털, 연안정비사업</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>기존은 고장 후 운영 중단 공지. 센서 기반 사전 예측으로 가동률을 높임</t>
+          <t>기존은 물리적 침식 등급 중심. 경제 피해를 결합해 투자 우선순위를 판단</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>AI 기술성이 잘 드러남, 결과가 명확</t>
+          <t>참신하고 기후 이슈와 연결</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>달성군 1곳 데이터라 일반화에 한계, 설비 도메인 지식 필요</t>
+          <t>해수욕장 주변 데이터 매칭 범위가 불확실, 인과 분석 난이도가 높음</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원장상</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
           <t>상</t>
         </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>4</v>
@@ -1354,13 +1352,15 @@
         <v>5</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>2025년 조사에서 229개 지구 중 C·D(우려·심각) 44.4%, 12개 지구는 오히려 악화</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>환경부 무공해차 통합누리집 충전소 현황, 충전기 설치 보조금, 민간 충전 앱</t>
+          <t>무공해차 누리집 충전소 현황, 기후부 공동주택 충전요금 개편 검토, 급속충전 확충 정책</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>여러 기관 결합으로 여러 상을 노릴 수 있음, 입지 선정형 결과물</t>
+          <t>여러 기관 데이터를 결합한 입지 선정형 결과물</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -1409,14 +1409,12 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>한전장상 (LH·SKT 후원상)</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K13" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L13" s="5" t="n">
         <v>4</v>
       </c>
@@ -1427,10 +1425,12 @@
         <v>4</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P13" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>공동주택 충전요금 급등·주차분쟁·관리비 갈등이 국민청원까지 확산, 구축 아파트는 주차·전력 용량 부족으로 설치 곤란</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>환경공단 영농폐기물 수거 보상금 제도, 마을 공동집하장</t>
+          <t>환경공단 수거보상금, 마을 공동집하장, 지자체 불법소각 단속·집중수거</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -1479,14 +1479,12 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>환경공단 후원상</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K14" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L14" s="5" t="n">
         <v>4</v>
       </c>
@@ -1497,10 +1495,12 @@
         <v>4</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14" s="5" t="n">
         <v>16</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>농촌 폐비닐 연 32만 톤 중 약 7만 톤이 방치, 산불의 상당수(쓰레기 소각 23.4%)가 소각에서 발생</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1549,28 +1549,28 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>LH 후원상</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
           <t>하</t>
         </is>
       </c>
+      <c r="K15" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L15" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" s="5" t="n">
         <v>15</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1579,68 +1579,68 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>스마트팜 기상재해 피해 예측</t>
+          <t>대구 공공배달앱 활성화 전략</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>폭염·태풍 등 이상기후로 시설작물 피해가 늘어남</t>
+          <t>여러 지자체 공공배달앱의 이용률이 저조하고 소상공인 수수료 부담은 여전</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>농가 환경·생육 실측 데이터와 기상특보·태풍 이력을 결합해 품목별 피해와 수익 영향을 예측하고 대응 매뉴얼을 제안</t>
+          <t>주문·리뷰·가맹점 데이터로 이탈 고객과 업종별 성과를 분석하고 상권·유동 데이터와 결합해 활성화 정책을 제안</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>EPIS: 스마트팜 우수농가 환경·생육·경영조사·기상·기상특보·태풍</t>
+          <t>경북대 첨단기술원: 대구로 주문·결제·배달·리뷰·가맹점·고객 / NICE 상권, SKT 유동인구</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>농촌진흥청 농업기상 재해 조기경보, 스마트팜코리아</t>
+          <t>소상공인 상권정보시스템, 경남 광역 공공배달앱 등 타 지자체 앱</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>지역 기상 기반 경보를 농가 실측 생육과 결합한 맞춤 예측으로 확장</t>
+          <t>공공앱 관점의 정책 분석</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>EPIS 데이터만으로 완결 가능</t>
+          <t>데이터 규모가 크고 분석 거리가 많음</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>2025년 BAST(기후·농산물)와 주제가 가까움</t>
+          <t>2022년 상반기 6개월 데이터라 시의성이 약하고, 2025년 슈올과 영역이 겹침</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>EPIS장상</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K16" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L16" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P16" s="5" t="n">
         <v>15</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>공공배달앱이 한때 30여 개에서 절반 이하로 줄었고, 대구로도 거래액 18.1%·주문 22.2% 감소로 구조 개편 기로</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1689,28 +1689,28 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>EPIS장상</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K17" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="L17" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17" s="5" t="n">
         <v>15</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1759,28 +1759,28 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>NIA장상 / 전북도지사상</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
           <t>상</t>
         </is>
       </c>
+      <c r="K18" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" s="5" t="n">
         <v>14</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1789,68 +1789,68 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>기상·노면 위험 구간 경보</t>
+          <t>스마트팜 기상재해 피해 예측</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>결빙·강우 시 고속도로 사고가 집중됨</t>
+          <t>폭염·태풍 등 이상기후로 시설작물 피해가 늘어남</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>사고 당시 기온·강수·노면·선형 정보로 위험 구간을 분류하고 기상 예보와 연동한 경보 구간을 제안</t>
+          <t>농가 환경·생육 실측 데이터와 기상특보·태풍 이력을 결합해 품목별 피해와 수익 영향을 예측하고 대응 매뉴얼을 제안</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>한국도로공사: 고속도로 교통사고(기온·강수·노면상태·선형·종단경사), 차량통행지표</t>
+          <t>EPIS: 스마트팜 우수농가 환경·생육·경영조사·기상·기상특보·태풍</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>도로 살얼음 위험구간 안내, 도로 기상정보 시스템</t>
+          <t>농진청 농업기상재해 조기경보시스템(155개 시·군, 필지별 위험도, 5만여 농가 이용)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>사고 이력 기반 구간별 위험 정밀화</t>
+          <t>지역 기상 기반 경보를 농가 실측 생육과 결합한 맞춤 예측으로 확장</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>데이터 준비가 쉬움</t>
+          <t>EPIS 데이터만으로 완결 가능</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>기존 서비스와 차별성이 약함</t>
+          <t>2025년 BAST(기후·농산물)와 주제가 가까움</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>도로공사장상</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" s="5" t="n">
         <v>14</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>2026년 여름 폭염·집중호우로 시설원예 피해, 스마트팜 고도화 장비 보급은 저조</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1859,68 +1859,68 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>축산물 가격 단기 예측</t>
+          <t>기상·노면 위험 구간 경보</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>소·돼지 가격 급등락으로 농가와 소비자 모두 피해</t>
+          <t>결빙·강우 시 고속도로 사고가 집중됨</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>경락가격과 외식·리테일 POS 소비를 결합해 단기 가격을 예측하고 수급 조절 신호를 제안</t>
+          <t>사고 당시 기온·강수·노면·선형 정보로 위험 구간을 분류하고 기상 예보와 연동한 경보 구간을 제안</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>EPIS: 소·돼지 도체 경락가격 / NICE지니데이터 외식·리테일 POS</t>
+          <t>한국도로공사: 고속도로 교통사고(기온·강수·노면상태·선형·종단경사), 차량통행지표</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>축산물품질평가원 축산유통정보, 한국농촌경제연구원 농업관측</t>
+          <t>도로 살얼음 위험구간 안내, 도로 기상정보 시스템</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>생산 중심 전망에 실제 소비 데이터를 결합</t>
+          <t>사고 이력 기반 구간별 위험 정밀화</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>예측 과제라 성과 지표가 명확</t>
+          <t>데이터 준비가 쉬움</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>가격 예측은 흔한 주제라 차별화가 어려움</t>
+          <t>기존 서비스와 차별성이 약함</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>EPIS장상 / NICE 후원상</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" s="5" t="n">
         <v>14</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1929,68 +1929,68 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>대구 공공배달앱 활성화 전략</t>
+          <t>축산물 가격 단기 예측</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>여러 지자체 공공배달앱의 이용률이 저조하고 소상공인 수수료 부담은 여전</t>
+          <t>소·돼지 가격 급등락으로 농가와 소비자 모두 피해</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>주문·리뷰·가맹점 데이터로 이탈 고객과 업종별 성과를 분석하고 상권·유동 데이터와 결합해 활성화 정책을 제안</t>
+          <t>경락가격과 외식·리테일 POS 소비를 결합해 단기 가격을 예측하고 수급 조절 신호를 제안</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원: 대구로 주문·결제·배달·리뷰·가맹점·고객 / NICE 상권, SKT 유동인구</t>
+          <t>EPIS: 소·돼지 도체 경락가격 / NICE지니데이터 외식·리테일 POS</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>소상공인 상권정보시스템, 민간 배달앱 사장님 분석 도구</t>
+          <t>축산물품질평가원 축산유통정보, 한국농촌경제연구원 농업관측</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>공공앱 관점의 정책 분석</t>
+          <t>생산 중심 전망에 실제 소비 데이터를 결합</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>데이터 규모가 크고 분석 거리가 많음</t>
+          <t>예측 과제라 성과 지표가 명확</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>2022년 상반기 6개월 데이터라 시의성이 약하고, 2025년 슈올과 영역이 겹침</t>
+          <t>가격 예측은 흔한 주제라 차별화가 어려움</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원장상</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K21" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="L21" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21" s="5" t="n">
         <v>14</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2039,28 +2039,28 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>환경공단 후원상</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
           <t>하</t>
         </is>
       </c>
+      <c r="K22" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="L22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" s="5" t="n">
         <v>14</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2109,28 +2109,28 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>건양대병원장상</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
           <t>상</t>
         </is>
       </c>
+      <c r="K23" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L23" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" s="5" t="n">
         <v>13</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2179,28 +2179,28 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>NIA장상 / NICE·신한 후원상</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K24" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="L24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>3</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P24" s="5" t="n">
         <v>13</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2249,28 +2249,28 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원장상</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K25" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="L25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>3</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" s="5" t="n">
         <v>13</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2319,28 +2319,28 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>환경공단 후원상</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
           <t>중</t>
         </is>
       </c>
+      <c r="K26" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="L26" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" s="5" t="n">
         <v>12</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2389,28 +2389,28 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>건양대병원장상</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
           <t>상</t>
         </is>
       </c>
+      <c r="K27" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="L27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" s="5" t="n">
         <v>11</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2425,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2507,46 +2507,34 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>노릴 상</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026년 최우수 9점은 주관·참여기관장상, 우수 5점은 후원기관·기업상이라 데이터 제공 기관 기준으로 표시</t>
+          <t>총점 → 공익성 → 차별성 순으로 정렬, 상위 3개는 노란색</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>순위</t>
+          <t>주의</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>총점 → 공익성 → 차별성 순으로 정렬, 상위 3개는 노란색</t>
+          <t>점수는 팀 판단용이며 공식 평가기준이 아님. 상위 15개는 2026-09-29 웹 검색으로 통계·기존 서비스를 확인했고, 나머지 11개의 기존 시스템은 일반 지식 기반이라 재확인 필요</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>주의</t>
+          <t>출처</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>점수와 '기존 시스템'은 공개 정보와 일반 지식 기반의 판단이며 공식 평가기준이 아님. 기존 서비스의 세부 현황은 제안서 작성 전에 다시 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>데이터: 대회 제공 데이터정의서 17종 / 수상작: 2025 데이터안심구역 활용 공동 경진대회 결과표 (사용자 제공)</t>
         </is>

--- a/docs/아이디어_후보_분석.xlsx
+++ b/docs/아이디어_후보_분석.xlsx
@@ -11,7 +11,7 @@
     <sheet name="평가기준" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'아이디어 추천순'!$A$1:$P$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'아이디어 추천순'!$A$1:$Q$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -509,6 +509,7 @@
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,6 +593,11 @@
           <t>근거 통계·실제 사례 (웹 검색 확인)</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>과거 수상작 중복 검토</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -662,6 +668,11 @@
           <t>2019~2023년 고속도로 사망자 832명 중 71%(591명)가 졸음·주시태만, 2026년 상반기 사망자 95명(전년 대비 35.7%↑) 중 71.6%가 졸음·주시태만 (한국도로공사)</t>
         </is>
       </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>부분: 2024 대상(서울 주차난 지수)과 '주차 부족 지수'로 보이지 않게 졸음·휴식 안전으로 프레이밍 필요. 2025 수상작 2팀은 고속도로 사고 데이터만 사용, 졸음쉼터 센서 활용작 없음</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -732,6 +743,11 @@
           <t>졸음쉼터 232곳 주차면 3,451면 중 대형 587면(17%)뿐이고 일부는 소형 2면을 합친 가변면. 화물차 사망사고 원인의 76%가 졸음·주시태만</t>
         </is>
       </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>부분: 2025 사고 데이터 활용작(구해줘헬기즈·탄탄대로)과 주제 다름, 졸음쉼터 센서 활용작 없음</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -802,6 +818,11 @@
           <t>최근 3년간 수소충전소 93곳이 고장으로 총 1,179일 운영 중단, 대구도 충전소 고장·정비 시 운행 차질 보도(2026.9)</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -870,6 +891,11 @@
       <c r="P5" s="7" t="inlineStr">
         <is>
           <t>부산은 9,000km 상수관 교체 시기 예측에 AI 도입, 관로 노후도 진단 AI·누수감지 IoT 기업 사례 다수</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -942,6 +968,11 @@
           <t>2026.1부터 수도권 생활폐기물 직매립 금지 시행, 66개 기초지자체 중 33곳이 공공소각 용량 부족으로 민간위탁 필요, 지방 전가 우려</t>
         </is>
       </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -1012,6 +1043,11 @@
           <t>복지사각지대 발굴시스템이 47종 위기정보를 쓰며, 복지부가 전기·수도 사용량 변화 추가와 입수주기 단축(2→1개월)을 추진 중</t>
         </is>
       </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -1082,6 +1118,11 @@
           <t>전북 청년 인구 연 약 8,000명 감소(4년간 3만여 명), 전주 제외 13개 시·군 소멸위험, 20대 순이동률 -3.1%로 최대</t>
         </is>
       </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>부분: 2025 Re:Career가 같은 사업장가입자 데이터 사용(여성 경력). 지역이동량 중심 청년 유출로 차별화</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1089,67 +1130,72 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>고령 보행자 교통사고 위험지수</t>
+          <t>사용후 배터리 재사용 매칭</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>초고령사회 진입으로 고령 보행자 사고와 사망 비중이 높음</t>
+          <t>전기차 보급 확대로 사용후 배터리가 급증할 예정인데, 재사용 판단과 수요 연결이 비효율적</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>사고 데이터와 연령별 유동인구, 필지·지형을 결합해 고령자 사고 위험지수를 만들고 노인보호구역 추가 지정 후보를 제안</t>
+          <t>성능평가 결과로 재사용 등급을 예측하고, 지역별 EV 충전 수요와 연결해 재사용 ESS(충전 보조 저장장치) 설치 후보지를 제안</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>한국도로교통공단 교통사고 / SKT 성·연령별 유동인구, LX 국토정보필지·DEM</t>
+          <t>한국환경공단: 전기차 폐배터리 성능평가 / 한국전력공사: 법정동별 시간대 EV 충전전력량</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>TAAS 교통사고분석시스템, 노인보호구역(30km/h) 제도</t>
+          <t>기후부 미래폐자원 거점수거센터, 민간 공급(연 1,500개 목표), 2027 탈거 전 성능평가 의무화</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>TAAS는 사고 결과 중심. 실제 고령 유동 노출량으로 나눈 위험도로 사고가 아직 적은 잠재 위험 지역까지 찾음</t>
+          <t>기존은 수거·평가까지만. 평가 결과와 지역 수요를 연결하는 순환 모델을 제시</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>공익성 높고 방법론이 명확</t>
+          <t>미래 이슈이고 경쟁팀이 적을 가능성이 큼</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>교통사고 데이터의 위치 정밀도 확인 필요</t>
+          <t>성능평가 데이터의 규모 확인 필요, 수요 매칭 논리를 설득력 있게 짜야 함</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" s="5" t="n">
+      <c r="N9" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="O9" s="5" t="n">
         <v>16</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2025년 보행 사망자 920명(3.8%↑) 중 65세 이상이 절반 이상, 고령 보행자 사고 11,498건(1.7%↑)</t>
+          <t>2021년부터 권역별 거점수거센터 6곳 운영, 1시간 신속 성능평가 도입, 대구·경남 거점 추가, 2027년 성능평가 의무화 예정</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1159,67 +1205,72 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>고속도로 사고 대응시간 단축</t>
+          <t>연안침식이 관광 경제에 주는 영향</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>사고 처리가 늦어지면 정체와 2차 사고가 늘어남</t>
+          <t>기후변화로 연안침식이 심해져 해수욕장 백사장이 줄고 지역 관광에도 영향</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>구급차 도착·인명구조·사고처리 소요시간과 도로점유 유형을 분석해 지연 구간을 찾고 견인·구급 거점 배치를 제안</t>
+          <t>해빈폭·단면적 변화와 주변 유동인구·카드매출을 결합해 침식의 경제 피해를 추정하고 복원 투자 우선순위를 제시</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>한국도로공사: 고속도로 교통사고(구급차도착·사고처리 소요시간, 도로점유), 차량통행지표</t>
+          <t>NIA: 연안침식 모니터링, 해수욕장 해빈폭·단면적 / SKT 유동인구, 신한카드 매출</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>도로공사 무료 긴급견인(1588-2504, 24시간), 2차사고 예방 행동요령 캠페인</t>
+          <t>해수부 연안침식 실태조사(A~D 등급), 연안포털, 연안정비사업</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>기존은 일괄 운영. 구간별 지연 원인을 데이터로 진단</t>
+          <t>기존은 물리적 침식 등급 중심. 경제 피해를 결합해 투자 우선순위를 판단</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>데이터 컬럼이 풍부하고 바로 분석 가능</t>
+          <t>참신하고 기후 이슈와 연결</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>2025년 구해줘헬기즈(중증외상 이송)와 겹쳐 차별성이 약함</t>
+          <t>해수욕장 주변 데이터 매칭 범위가 불확실, 인과 분석 난이도가 높음</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="N10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>16</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>2차사고 치사율이 일반사고의 약 6배, 최근 5년 사망자 784명 중 138명(18%)이 2차사고</t>
+          <t>2025년 조사에서 229개 지구 중 C·D(우려·심각) 44.4%, 12개 지구는 오히려 악화</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1229,47 +1280,47 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>사용후 배터리 재사용 매칭</t>
+          <t>EV 충전 수요·공급 격차 지수</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>전기차 보급 확대로 사용후 배터리가 급증할 예정인데, 재사용 판단과 수요 연결이 비효율적</t>
+          <t>전기차는 늘지만 공동주택·임대주택 거주자는 충전기 부족과 주차 갈등을 겪음</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>성능평가 결과로 재사용 등급을 예측하고, 지역별 EV 충전 수요와 연결해 재사용 ESS(충전 보조 저장장치) 설치 후보지를 제안</t>
+          <t>법정동별 시간대 충전량(가정 vs 충전사업자)으로 충전 수요를 보고, 임대주택 분포·유동인구와 결합해 충전 인프라 부족 지역을 도출</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>한국환경공단: 전기차 폐배터리 성능평가 / 한국전력공사: 법정동별 시간대 EV 충전전력량</t>
+          <t>한국전력공사: EV 충전전력량 2종 / LH 건설임대주택, SKT 유동인구, LX 국토정보필지</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>기후부 미래폐자원 거점수거센터, 민간 공급(연 1,500개 목표), 2027 탈거 전 성능평가 의무화</t>
+          <t>무공해차 누리집 충전소 현황, 기후부 공동주택 충전요금 개편 검토, 급속충전 확충 정책</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>기존은 수거·평가까지만. 평가 결과와 지역 수요를 연결하는 순환 모델을 제시</t>
+          <t>기존은 설치 대수 기준. 실제 시간대별 사용량으로 수요를 보고 임대주택 거주자의 충전 소외를 조명</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>미래 이슈이고 경쟁팀이 적을 가능성이 큼</t>
+          <t>여러 기관 데이터를 결합한 입지 선정형 결과물</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>성능평가 데이터의 규모 확인 필요, 수요 매칭 논리를 설득력 있게 짜야 함</t>
+          <t>법정동 단위 집계라 분석이 거침</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
@@ -1279,17 +1330,22 @@
         <v>4</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="5" t="n">
         <v>16</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2021년부터 권역별 거점수거센터 6곳 운영, 1시간 신속 성능평가 도입, 대구·경남 거점 추가, 2027년 성능평가 의무화 예정</t>
+          <t>공동주택 충전요금 급등·주차분쟁·관리비 갈등이 국민청원까지 확산, 구축 아파트는 주차·전력 용량 부족으로 설치 곤란</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1299,47 +1355,47 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>연안침식이 관광 경제에 주는 영향</t>
+          <t>영농폐비닐 수거 최적화</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>기후변화로 연안침식이 심해져 해수욕장 백사장이 줄고 지역 관광에도 영향</t>
+          <t>영농폐비닐이 불법 소각·방치되어 환경오염과 산불 위험을 키움</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>해빈폭·단면적 변화와 주변 유동인구·카드매출을 결합해 침식의 경제 피해를 추정하고 복원 투자 우선순위를 제시</t>
+          <t>수거 실적과 재고, 농지 필지로 마을별 발생량을 추정하고 집하장 위치와 수거 일정을 최적화</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>NIA: 연안침식 모니터링, 해수욕장 해빈폭·단면적 / SKT 유동인구, 신한카드 매출</t>
+          <t>한국환경공단: 영농폐기물 수거실적, 전북 수거사업소 재고, 영농폐비닐 재활용생산품 / LX 국토정보필지</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>해수부 연안침식 실태조사(A~D 등급), 연안포털, 연안정비사업</t>
+          <t>환경공단 수거보상금, 마을 공동집하장, 지자체 불법소각 단속·집중수거</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>기존은 물리적 침식 등급 중심. 경제 피해를 결합해 투자 우선순위를 판단</t>
+          <t>기존은 신고·보상 기반 사후 수거. 발생량 예측 기반 선제 수거</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>참신하고 기후 이슈와 연결</t>
+          <t>경쟁이 약할 가능성, 경로 최적화 결과가 눈에 보임</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>해수욕장 주변 데이터 매칭 범위가 불확실, 인과 분석 난이도가 높음</t>
+          <t>2025년 HMH의 '재배치·경로' 형식과 비슷하게 보일 수 있음</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
@@ -1349,17 +1405,22 @@
         <v>4</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>16</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>2025년 조사에서 229개 지구 중 C·D(우려·심각) 44.4%, 12개 지구는 오히려 악화</t>
+          <t>농촌 폐비닐 연 32만 톤 중 약 7만 톤이 방치, 산불의 상당수(쓰레기 소각 23.4%)가 소각에서 발생</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1369,42 +1430,42 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>EV 충전 수요·공급 격차 지수</t>
+          <t>고령 보행자 교통사고 위험지수</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>전기차는 늘지만 공동주택·임대주택 거주자는 충전기 부족과 주차 갈등을 겪음</t>
+          <t>초고령사회 진입으로 고령 보행자 사고와 사망 비중이 높음</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>법정동별 시간대 충전량(가정 vs 충전사업자)으로 충전 수요를 보고, 임대주택 분포·유동인구와 결합해 충전 인프라 부족 지역을 도출</t>
+          <t>사고 데이터와 연령별 유동인구, 필지·지형을 결합해 고령자 사고 위험지수를 만들고 노인보호구역 추가 지정 후보를 제안</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>한국전력공사: EV 충전전력량 2종 / LH 건설임대주택, SKT 유동인구, LX 국토정보필지</t>
+          <t>한국도로교통공단 교통사고 / SKT 성·연령별 유동인구, LX 국토정보필지·DEM</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>무공해차 누리집 충전소 현황, 기후부 공동주택 충전요금 개편 검토, 급속충전 확충 정책</t>
+          <t>TAAS 교통사고분석시스템, 노인보호구역(30km/h) 제도</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>기존은 설치 대수 기준. 실제 시간대별 사용량으로 수요를 보고 임대주택 거주자의 충전 소외를 조명</t>
+          <t>TAAS는 사고 결과 중심. 실제 고령 유동 노출량으로 나눈 위험도로 사고가 아직 적은 잠재 위험 지역까지 찾음</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>여러 기관 데이터를 결합한 입지 선정형 결과물</t>
+          <t>공익성 높고 방법론이 명확</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>법정동 단위 집계라 분석이 거침</t>
+          <t>교통사고 데이터의 위치 정밀도 확인 필요</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1413,23 +1474,28 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>공동주택 충전요금 급등·주차분쟁·관리비 갈등이 국민청원까지 확산, 구축 아파트는 주차·전력 용량 부족으로 설치 곤란</t>
+          <t>2025년 보행 사망자 920명(3.8%↑) 중 65세 이상이 절반 이상, 고령 보행자 사고 11,498건(1.7%↑)</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>부분: 2024 교통약자 보행 내비(every-map), 2025 노인 여가공간(빈터뷰)과 대상층이 겹침</t>
         </is>
       </c>
     </row>
@@ -1439,42 +1505,42 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>영농폐비닐 수거 최적화</t>
+          <t>대구 공공배달앱 활성화 전략</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>영농폐비닐이 불법 소각·방치되어 환경오염과 산불 위험을 키움</t>
+          <t>여러 지자체 공공배달앱의 이용률이 저조하고 소상공인 수수료 부담은 여전</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>수거 실적과 재고, 농지 필지로 마을별 발생량을 추정하고 집하장 위치와 수거 일정을 최적화</t>
+          <t>주문·리뷰·가맹점 데이터로 이탈 고객과 업종별 성과를 분석하고 상권·유동 데이터와 결합해 활성화 정책을 제안</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>한국환경공단: 영농폐기물 수거실적, 전북 수거사업소 재고, 영농폐비닐 재활용생산품 / LX 국토정보필지</t>
+          <t>경북대 첨단기술원: 대구로 주문·결제·배달·리뷰·가맹점·고객 / NICE 상권, SKT 유동인구</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>환경공단 수거보상금, 마을 공동집하장, 지자체 불법소각 단속·집중수거</t>
+          <t>소상공인 상권정보시스템, 경남 광역 공공배달앱 등 타 지자체 앱</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>기존은 신고·보상 기반 사후 수거. 발생량 예측 기반 선제 수거</t>
+          <t>공공앱 관점의 정책 분석</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>경쟁이 약할 가능성, 경로 최적화 결과가 눈에 보임</t>
+          <t>데이터 규모가 크고 분석 거리가 많음</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>2025년 HMH의 '재배치·경로' 형식과 비슷하게 보일 수 있음</t>
+          <t>2022년 상반기 6개월 데이터라 시의성이 약하고, 2025년 슈올과 영역이 겹침</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1489,17 +1555,22 @@
         <v>4</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>농촌 폐비닐 연 32만 톤 중 약 7만 톤이 방치, 산불의 상당수(쓰레기 소각 23.4%)가 소각에서 발생</t>
+          <t>공공배달앱이 한때 30여 개에서 절반 이하로 줄었고, 대구로도 거래액 18.1%·주문 22.2% 감소로 구조 개편 기로</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>부분: 2025 슈올(지역 매출·옥외광고), 삼정(배달매출) 과 소상공인 영역 인접</t>
         </is>
       </c>
     </row>
@@ -1509,54 +1580,54 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>임대주택 주거비 과부담 단지 발굴</t>
+          <t>토마토 생육 이미지 AI</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>임대료·관리비·에너지비 상승으로 저소득 임차가구의 부담이 커짐</t>
+          <t>스마트팜 보급에도 생육 판단은 농민 경험에 의존</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>관리비·월임대료와 지역 소득을 결합해 주거비 과부담 지수를 만들고 지원 우선 단지를 선정</t>
+          <t>토마토 이미지와 생육·환경 데이터로 생육 단계와 수확량을 예측하는 모델</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>LH 건설임대주택 계약·관리비 / 경북개발공사 공공임대주택 월임대료 / KCB 소득</t>
+          <t>EPIS: 토마토 9주차 이미지, 스마트팜 생육·환경</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>주거급여, 에너지바우처, 공동주택관리정보시스템(K-apt) 관리비 공개</t>
+          <t>스마트팜 생육 측정 서비스, 민간 농업 AI</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>개별 가구 신청 기반 지원을 단지 단위 선제 발굴로 전환</t>
+          <t>이미지와 환경 데이터를 결합한 모델</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>데이터 결합이 비교적 쉬움</t>
+          <t>기술 결과물이 명확</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>2025년 에너지빈곤(에.격.그), VULNERGY와 비슷한 '취약지수' 계열</t>
+          <t>참신성이 보통이고 이미지 규모에 따라 성능 한계</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>3</v>
@@ -1570,6 +1641,11 @@
       <c r="P15" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2025 코코팜이 스마트팜 데이터를 썼지만 주제는 전력요금</t>
         </is>
       </c>
     </row>
@@ -1579,67 +1655,72 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>대구 공공배달앱 활성화 전략</t>
+          <t>전북 산업 고용 취약도 진단</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>여러 지자체 공공배달앱의 이용률이 저조하고 소상공인 수수료 부담은 여전</t>
+          <t>지역 산업 쇠퇴가 일자리 감소와 인구 유출로 이어짐</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>주문·리뷰·가맹점 데이터로 이탈 고객과 업종별 성과를 분석하고 상권·유동 데이터와 결합해 활성화 정책을 제안</t>
+          <t>산업생태계 데이터와 연금 사업장·가입자 변동을 결합해 고용 충격에 취약한 산업·지역을 진단</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>경북대 첨단기술원: 대구로 주문·결제·배달·리뷰·가맹점·고객 / NICE 상권, SKT 유동인구</t>
+          <t>NIA: 3년간 산업 생태계 분석 / 전북·국민연금: 사업장, 사업장가입자</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>소상공인 상권정보시스템, 경남 광역 공공배달앱 등 타 지자체 앱</t>
+          <t>지역산업 진흥계획, 고용위기지역 지정</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>공공앱 관점의 정책 분석</t>
+          <t>사업장 단위 고용 변동으로 조기 진단</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>데이터 규모가 크고 분석 거리가 많음</t>
+          <t>7번(청년 이탈)과 묶으면 시너지</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>2022년 상반기 6개월 데이터라 시의성이 약하고, 2025년 슈올과 영역이 겹침</t>
+          <t>두 데이터 간 결합 키 확인 필요</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
         <v>4</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N16" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="O16" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>공공배달앱이 한때 30여 개에서 절반 이하로 줄었고, 대구로도 거래액 18.1%·주문 22.2% 감소로 구조 개편 기로</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>부분: 2025 Re:Career와 같은 연금 데이터 사용</t>
         </is>
       </c>
     </row>
@@ -1649,67 +1730,72 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>토마토 생육 이미지 AI</t>
+          <t>기상·노면 위험 구간 경보</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>스마트팜 보급에도 생육 판단은 농민 경험에 의존</t>
+          <t>결빙·강우 시 고속도로 사고가 집중됨</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>토마토 이미지와 생육·환경 데이터로 생육 단계와 수확량을 예측하는 모델</t>
+          <t>사고 당시 기온·강수·노면·선형 정보로 위험 구간을 분류하고 기상 예보와 연동한 경보 구간을 제안</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>EPIS: 토마토 9주차 이미지, 스마트팜 생육·환경</t>
+          <t>한국도로공사: 고속도로 교통사고(기온·강수·노면상태·선형·종단경사), 차량통행지표</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>스마트팜 생육 측정 서비스, 민간 농업 AI</t>
+          <t>도로 살얼음 위험구간 안내, 도로 기상정보 시스템</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>이미지와 환경 데이터를 결합한 모델</t>
+          <t>사고 이력 기반 구간별 위험 정밀화</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>기술 결과물이 명확</t>
+          <t>데이터 준비가 쉬움</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>참신성이 보통이고 이미지 규모에 따라 성능 한계</t>
+          <t>기존 서비스와 차별성이 약함</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>부분: 2025 탄탄대로가 같은 고속도로 사고 데이터 사용(자율주행 지표)</t>
         </is>
       </c>
     </row>
@@ -1719,60 +1805,60 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>전북 산업 고용 취약도 진단</t>
+          <t>폐전자제품 회수 사각지대</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>지역 산업 쇠퇴가 일자리 감소와 인구 유출로 이어짐</t>
+          <t>폐가전의 무단 투기와 자원 손실 문제</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>산업생태계 데이터와 연금 사업장·가입자 변동을 결합해 고용 충격에 취약한 산업·지역을 진단</t>
+          <t>회수 실적을 인구·유동과 비교해 회수율이 낮은 지역을 찾고 수거 거점을 제안</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>NIA: 3년간 산업 생태계 분석 / 전북·국민연금: 사업장, 사업장가입자</t>
+          <t>한국환경공단: 폐전기전자제품 회수·재활용 실적 / SKT 유동인구</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>지역산업 진흥계획, 고용위기지역 지정</t>
+          <t>폐가전 무상방문수거 서비스</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>사업장 단위 고용 변동으로 조기 진단</t>
+          <t>지역별 회수 사각지대를 데이터로 진단</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>7번(청년 이탈)과 묶으면 시너지</t>
+          <t>주제가 명확하고 분석이 쉬움</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>두 데이터 간 결합 키 확인 필요</t>
+          <t>임팩트가 크지 않음</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="N18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18" s="5" t="n">
         <v>14</v>
@@ -1780,6 +1866,11 @@
       <c r="P18" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1789,67 +1880,72 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>스마트팜 기상재해 피해 예측</t>
+          <t>대전 내분비질환 위험지도</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>폭염·태풍 등 이상기후로 시설작물 피해가 늘어남</t>
+          <t>당뇨·고혈압 등 만성질환이 늘고 지역별 관리 격차가 있음</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>농가 환경·생육 실측 데이터와 기상특보·태풍 이력을 결합해 품목별 피해와 수익 영향을 예측하고 대응 매뉴얼을 제안</t>
+          <t>검진·진료 코호트로 시군구별 만성질환 위험을 분석하고 생활환경(외식 소비 등)과의 관계를 제시</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>EPIS: 스마트팜 우수농가 환경·생육·경영조사·기상·기상특보·태풍</t>
+          <t>건양대병원: 내분비질환 검진·진료 코호트 / NICE 외식 POS</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>농진청 농업기상재해 조기경보시스템(155개 시·군, 필지별 위험도, 5만여 농가 이용)</t>
+          <t>국민건강보험공단 건강위험도 평가, 지역 보건소 만성질환 관리</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>지역 기상 기반 경보를 농가 실측 생육과 결합한 맞춤 예측으로 확장</t>
+          <t>병원 실측 데이터 기반 지역 위험 분석</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>EPIS 데이터만으로 완결 가능</t>
+          <t>의료 데이터라 희소성이 있음</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>2025년 BAST(기후·농산물)와 주제가 가까움</t>
+          <t>대전 시군구 단위로 범위가 좁고, 의료 도메인 지식 필요</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
         <v>4</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="O19" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026년 여름 폭염·집중호우로 시설원예 피해, 스마트팜 고도화 장비 보급은 저조</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1859,67 +1955,72 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>기상·노면 위험 구간 경보</t>
+          <t>대구 교차로 신호 개선 우선순위</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>결빙·강우 시 고속도로 사고가 집중됨</t>
+          <t>도심 교차로 정체와 사고</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>사고 당시 기온·강수·노면·선형 정보로 위험 구간을 분류하고 기상 예보와 연동한 경보 구간을 제안</t>
+          <t>ITS 교차로별 교통량으로 혼잡 교차로를 선별하고 신호 개선 우선순위를 제안</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>한국도로공사: 고속도로 교통사고(기온·강수·노면상태·선형·종단경사), 차량통행지표</t>
+          <t>경북대 첨단기술원: 대구 ITS 교통량·교차로·카메라·구역</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>도로 살얼음 위험구간 안내, 도로 기상정보 시스템</t>
+          <t>대구 교통정보센터, 스마트 신호제어 사업</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>사고 이력 기반 구간별 위험 정밀화</t>
+          <t>우선순위 선정의 근거를 데이터로 제시</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>데이터 준비가 쉬움</t>
+          <t>교통량 데이터가 명확</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>기존 서비스와 차별성이 약함</t>
+          <t>기존 ITS 운영과 차별성이 약함</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1929,42 +2030,42 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>축산물 가격 단기 예측</t>
+          <t>하수·폐수 수질 이상 조기탐지</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>소·돼지 가격 급등락으로 농가와 소비자 모두 피해</t>
+          <t>처리시설의 방류 수질 이상은 하천 오염으로 이어짐</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>경락가격과 외식·리테일 POS 소비를 결합해 단기 가격을 예측하고 수급 조절 신호를 제안</t>
+          <t>유입·유출 수질 분석 데이터로 이상 패턴을 탐지하는 모델</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>EPIS: 소·돼지 도체 경락가격 / NICE지니데이터 외식·리테일 POS</t>
+          <t>한국환경공단: 생활하수·공장폐수 유입유출 수질분석</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>축산물품질평가원 축산유통정보, 한국농촌경제연구원 농업관측</t>
+          <t>수질원격감시체계(TMS)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>생산 중심 전망에 실제 소비 데이터를 결합</t>
+          <t>처리 효율 이상의 조기탐지</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>예측 과제라 성과 지표가 명확</t>
+          <t>모델링이 명확</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>가격 예측은 흔한 주제라 차별화가 어려움</t>
+          <t>TMS와 차별성이 약함</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1979,17 +2080,22 @@
         <v>4</v>
       </c>
       <c r="M21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="O21" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
@@ -1999,47 +2105,47 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>폐전자제품 회수 사각지대</t>
+          <t>안저 영상 당뇨망막병증 선별 AI</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>폐가전의 무단 투기와 자원 손실 문제</t>
+          <t>당뇨망막병증 조기 발견이 늦어 실명 위험</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>회수 실적을 인구·유동과 비교해 회수율이 낮은 지역을 찾고 수거 거점을 제안</t>
+          <t>안저 이미지로 질환 선별 모델 개발</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>한국환경공단: 폐전기전자제품 회수·재활용 실적 / SKT 유동인구</t>
+          <t>건양대병원: 안저 이미지(황반변성·당뇨망막병증)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>폐가전 무상방문수거 서비스</t>
+          <t>상용 안저 판독 AI 의료기기</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>지역별 회수 사각지대를 데이터로 진단</t>
+          <t>지역 병원 데이터 기반 검증</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>주제가 명확하고 분석이 쉬움</t>
+          <t>데이터 규모가 큼(5.56GB)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>임팩트가 크지 않음</t>
+          <t>이미 상용화된 분야라 차별성이 낮고 제안서형 대회와 성격이 다름</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
@@ -2049,372 +2155,27 @@
         <v>4</v>
       </c>
       <c r="M22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="O22" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>대전 내분비질환 위험지도</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>당뇨·고혈압 등 만성질환이 늘고 지역별 관리 격차가 있음</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>검진·진료 코호트로 시군구별 만성질환 위험을 분석하고 생활환경(외식 소비 등)과의 관계를 제시</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>건양대병원: 내분비질환 검진·진료 코호트 / NICE 외식 POS</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>국민건강보험공단 건강위험도 평가, 지역 보건소 만성질환 관리</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>병원 실측 데이터 기반 지역 위험 분석</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>의료 데이터라 희소성이 있음</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>대전 시군구 단위로 범위가 좁고, 의료 도메인 지식 필요</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>오프라인 소상공인 온라인 전환 지원</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>온라인 소비 확대로 오프라인 소상공인 매출이 감소</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>연령별 온라인 매출과 오프라인 POS·카드 매출을 비교해 온라인 전환 효과가 큰 업종과 지역을 제안</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>NIA: 온라인 쇼핑몰 연령별 매출 / NICE POS, 신한카드 매출</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>소상공인시장진흥공단 온라인 판로 지원</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>지원 대상 선정을 데이터 기반으로</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>상권 계열 데이터가 풍부</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>상권 분석 주제가 흔함 (2025년 SEED, 슈올)</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>대구 교차로 신호 개선 우선순위</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>도심 교차로 정체와 사고</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>ITS 교차로별 교통량으로 혼잡 교차로를 선별하고 신호 개선 우선순위를 제안</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>경북대 첨단기술원: 대구 ITS 교통량·교차로·카메라·구역</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>대구 교통정보센터, 스마트 신호제어 사업</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>우선순위 선정의 근거를 데이터로 제시</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>교통량 데이터가 명확</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>기존 ITS 운영과 차별성이 약함</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>하수·폐수 수질 이상 조기탐지</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>처리시설의 방류 수질 이상은 하천 오염으로 이어짐</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>유입·유출 수질 분석 데이터로 이상 패턴을 탐지하는 모델</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>한국환경공단: 생활하수·공장폐수 유입유출 수질분석</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>수질원격감시체계(TMS)</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>처리 효율 이상의 조기탐지</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>모델링이 명확</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>TMS와 차별성이 약함</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>안저 영상 당뇨망막병증 선별 AI</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>당뇨망막병증 조기 발견이 늦어 실명 위험</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>안저 이미지로 질환 선별 모델 개발</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>건양대병원: 안저 이미지(황반변성·당뇨망막병증)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>상용 안저 판독 AI 의료기기</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>지역 병원 데이터 기반 검증</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>데이터 규모가 큼(5.56GB)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>이미 상용화된 분야라 차별성이 낮고 제안서형 대회와 성격이 다름</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>없음: 2024·2025 확인된 수상작과 주제·데이터 중복 없음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P27"/>
+  <autoFilter ref="A1:Q22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2425,7 +2186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2507,34 +2268,46 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>순위</t>
+          <t>과거 수상작</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>총점 → 공익성 → 차별성 순으로 정렬, 상위 3개는 노란색</t>
+          <t>2025년 수상작 17개(사용자 제공)와 2024년 확인된 수상작(대상 주차난 지수, 전북 식품사막 이동형 저장소, 교통약자 보행 내비, 은행 점포 폐쇄 영향)과 비교. 겹침이 큰 5개(사고 대응시간, 임대주택 주거비, 스마트팜 기상재해, 축산물 가격, 소상공인 온라인 전환)는 목록에서 제외. 2023년 수상작은 확인 불가</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>주의</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>점수는 팀 판단용이며 공식 평가기준이 아님. 상위 15개는 2026-09-29 웹 검색으로 통계·기존 서비스를 확인했고, 나머지 11개의 기존 시스템은 일반 지식 기반이라 재확인 필요</t>
+          <t>총점 → 공익성 → 차별성 순으로 정렬, 상위 3개는 노란색</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>점수는 팀 판단용이며 공식 평가기준이 아님. 상위 15개는 2026-09-29 웹 검색으로 통계·기존 서비스를 확인했고, 나머지 11개의 기존 시스템은 일반 지식 기반이라 재확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>데이터: 대회 제공 데이터정의서 17종 / 수상작: 2025 데이터안심구역 활용 공동 경진대회 결과표 (사용자 제공)</t>
         </is>
